--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.67359787001356</v>
+        <v>3.846959653877204</v>
       </c>
       <c r="D2" t="n">
-        <v>42.43756522856972</v>
+        <v>6.89610434964258</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50454988371476</v>
+        <v>2.03198935610365</v>
       </c>
       <c r="F2" t="n">
-        <v>11.50400260463074</v>
+        <v>1.869400423252496</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.32068217284363</v>
+        <v>7.85211085308709</v>
       </c>
       <c r="D3" t="n">
-        <v>46.39215395499724</v>
+        <v>7.538725017687052</v>
       </c>
       <c r="E3" t="n">
-        <v>12.50454988371476</v>
+        <v>2.03198935610365</v>
       </c>
       <c r="F3" t="n">
-        <v>11.50400260463074</v>
+        <v>1.869400423252496</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.24823905655838</v>
+        <v>3.290338846690736</v>
       </c>
       <c r="D4" t="n">
-        <v>20.25269365665489</v>
+        <v>3.29106271920642</v>
       </c>
       <c r="E4" t="n">
-        <v>12.50454988371476</v>
+        <v>2.03198935610365</v>
       </c>
       <c r="F4" t="n">
-        <v>11.50400260463074</v>
+        <v>1.869400423252496</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
